--- a/data/main/sheets/batch_02.xlsx
+++ b/data/main/sheets/batch_02.xlsx
@@ -467,19 +467,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_78</t>
+          <t xml:space="preserve">multiple_169</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the average temperature in Austin for the next 3 days in Celsius.</t>
+          <t xml:space="preserve">What is the musical scale associated with C sharp major?</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Austin
-days = 3
-temp_unit = Celsius</t>
+          <t xml:space="preserve">key = C sharp</t>
         </is>
       </c>
       <c r="D3" s="6"/>
@@ -491,17 +489,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_169</t>
+          <t xml:space="preserve">simple_python_55</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the musical scale associated with C sharp major?</t>
+          <t xml:space="preserve">Find me detailed information about the structure of human cell</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">key = C sharp</t>
+          <t xml:space="preserve">cell_type = human</t>
         </is>
       </c>
       <c r="D4" s="6"/>
@@ -513,17 +511,19 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_55</t>
+          <t xml:space="preserve">multiple_78</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me detailed information about the structure of human cell</t>
+          <t xml:space="preserve">Get me information about Natural History Museum in London including timings, exhibitions, and accessibility.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cell_type = human</t>
+          <t xml:space="preserve">museum = Natural History Museum
+city = London
+features = timings, exhibitions, accessibility</t>
         </is>
       </c>
       <c r="D5" s="6"/>
@@ -535,19 +535,18 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_78</t>
+          <t xml:space="preserve">simple_python_179</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get me information about Natural History Museum in London including timings, exhibitions, and accessibility.</t>
+          <t xml:space="preserve">Find the latest court case between Apple and Samsung occured in USA.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">museum = Natural History Museum
-city = London
-features = timings, exhibitions, accessibility</t>
+          <t xml:space="preserve">company1 = Apple
+company2 = Samsung</t>
         </is>
       </c>
       <c r="D6" s="6"/>
@@ -559,18 +558,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_179</t>
+          <t xml:space="preserve">multiple_45</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the latest court case between Apple and Samsung occured in USA.</t>
+          <t xml:space="preserve">Calculate how many years ago was the Ice age?</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company1 = Apple
-company2 = Samsung</t>
+          <t xml:space="preserve">era_name = Ice age</t>
         </is>
       </c>
       <c r="D7" s="6"/>
@@ -582,17 +580,18 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_45</t>
+          <t xml:space="preserve">simple_python_85</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calculate how many years ago was the Ice age?</t>
+          <t xml:space="preserve">What's the approximate distance between Boston, MA, and Washington, D.C. in mile?</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">era_name = Ice age</t>
+          <t xml:space="preserve">start_location = Boston, MA
+end_location = Washington, D.C.</t>
         </is>
       </c>
       <c r="D8" s="6"/>
@@ -604,18 +603,18 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_85</t>
+          <t xml:space="preserve">simple_python_218</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the approximate distance between Boston, MA, and Washington, D.C. in mile?</t>
+          <t xml:space="preserve">Given patient with id 546382, retrieve their brain MRI report with the status 'concluded'.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_location = Boston, MA
-end_location = Washington, D.C.</t>
+          <t xml:space="preserve">patient_id = 546382
+status = concluded</t>
         </is>
       </c>
       <c r="D9" s="6"/>
@@ -627,18 +626,20 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_218</t>
+          <t xml:space="preserve">multiple_93</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Given patient with id 546382, retrieve their brain MRI report with the status 'concluded'.</t>
+          <t xml:space="preserve">Book a deluxe room for 2 nights at the Marriott hotel in New York and add breakfast as an extra service</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id = 546382
-status = concluded</t>
+          <t xml:space="preserve">location = New York
+roomType = deluxe
+nights = 2
+additional_services = breakfast</t>
         </is>
       </c>
       <c r="D10" s="6"/>
@@ -650,20 +651,19 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_93</t>
+          <t xml:space="preserve">simple_python_213</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book a deluxe room for 2 nights at the Marriott hotel in New York and add breakfast as an extra service</t>
+          <t xml:space="preserve">Book a direct flight from San Francisco to London for 2022-04-27 afternoon</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York
-roomType = deluxe
-nights = 2
-additional_services = breakfast</t>
+          <t xml:space="preserve">departure_location = San Francisco
+destination_location = London
+date = 2022-04-27</t>
         </is>
       </c>
       <c r="D11" s="6"/>
@@ -675,19 +675,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_213</t>
+          <t xml:space="preserve">multiple_155</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book a direct flight from San Francisco to London for 2022-04-27 afternoon</t>
+          <t xml:space="preserve">Who discovered the neutron? Give me detail information.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">departure_location = San Francisco
-destination_location = London
-date = 2022-04-27</t>
+          <t xml:space="preserve">discovery = neutron</t>
         </is>
       </c>
       <c r="D12" s="6"/>
@@ -699,17 +697,19 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_155</t>
+          <t xml:space="preserve">simple_python_284</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who discovered the neutron? Give me detail information.</t>
+          <t xml:space="preserve">Get information about the pop concerts in New York for next month.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">discovery = neutron</t>
+          <t xml:space="preserve">location = New York
+date = next month
+genre = pop</t>
         </is>
       </c>
       <c r="D13" s="6"/>
@@ -721,19 +721,18 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_284</t>
+          <t xml:space="preserve">multiple_82</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get information about the pop concerts in New York for next month.</t>
+          <t xml:space="preserve">Play a song in C Major key at tempo 120 bpm.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York
-date = next month
-genre = pop</t>
+          <t xml:space="preserve">key = C Major
+tempo = 120</t>
         </is>
       </c>
       <c r="D14" s="6"/>
@@ -745,18 +744,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_82</t>
+          <t xml:space="preserve">simple_python_54</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Play a song in C Major key at tempo 120 bpm.</t>
+          <t xml:space="preserve">Identify the protein sequence of a given human gene 'BRCA1'.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">key = C Major
-tempo = 120</t>
+          <t xml:space="preserve">gene = BRCA1</t>
         </is>
       </c>
       <c r="D15" s="6"/>
@@ -768,17 +766,18 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_54</t>
+          <t xml:space="preserve">simple_python_73</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identify the protein sequence of a given human gene 'BRCA1'.</t>
+          <t xml:space="preserve">What's the projected population growth in United States in the next 20 years?</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gene = BRCA1</t>
+          <t xml:space="preserve">country = United States
+years = 20</t>
         </is>
       </c>
       <c r="D16" s="6"/>
@@ -790,19 +789,18 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_160</t>
+          <t xml:space="preserve">multiple_187</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who was the victim in the case docket numbered 2022/AL2562 in California?</t>
+          <t xml:space="preserve">Check the price of tomatoes and lettuce at the Whole Foods in Los Angeles.</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">docket = 2022/AL2562
-court = California
-info_type = victim</t>
+          <t xml:space="preserve">location = Los Angeles
+items = tomatoes, lettuce</t>
         </is>
       </c>
       <c r="D17" s="6"/>
@@ -814,18 +812,18 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_187</t>
+          <t xml:space="preserve">simple_python_147</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check the price of tomatoes and lettuce at the Whole Foods in Los Angeles.</t>
+          <t xml:space="preserve">Retrieve stock prices of Microsoft and Google for the last 2 weeks.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Los Angeles
-items = tomatoes, lettuce</t>
+          <t xml:space="preserve">companies = Microsoft, Google
+duration = 2 weeks</t>
         </is>
       </c>
       <c r="D18" s="6"/>
@@ -837,18 +835,19 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_147</t>
+          <t xml:space="preserve">multiple_184</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retrieve stock prices of Microsoft and Google for the last 2 weeks.</t>
+          <t xml:space="preserve">Give me a recipe for a vegetarian pasta with cheese for 2 servings.</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">companies = Microsoft, Google
-duration = 2 weeks</t>
+          <t xml:space="preserve">dietary_restriction = vegetarian
+ingredients = pasta, cheese
+servings = 2</t>
         </is>
       </c>
       <c r="D19" s="6"/>
@@ -860,19 +859,19 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_184</t>
+          <t xml:space="preserve">simple_python_344</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give me a recipe for a vegetarian pasta with cheese for 2 servings.</t>
+          <t xml:space="preserve">What's the power rating for the Weapon 'Guardian Sword+' in the game 'Legend of Zelda: Breath of the Wild'?</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dietary_restriction = vegetarian
-ingredients = pasta, cheese
-servings = 2</t>
+          <t xml:space="preserve">game = Legend of Zelda: Breath of the Wild
+item = Guardian Sword+
+stat = power rating</t>
         </is>
       </c>
       <c r="D20" s="6"/>
@@ -884,18 +883,20 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_331</t>
+          <t xml:space="preserve">simple_python_340</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the top chess players in New York with a rating above 2300.</t>
+          <t xml:space="preserve">Determine the winner in a Poker game with John having a Hand of 8♥, 10♥, J♥, Q♥, K♥ and Mike having 9♠, J♠, 10♠, Q♠, K♠.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York
-minimum_rating = 2300</t>
+          <t xml:space="preserve">player1 = John
+hand1 = 8♥, 10♥, J♥, Q♥, K♥
+player2 = Mike
+hand2 = 9♠, J♠, 10♠, Q♠, K♠</t>
         </is>
       </c>
       <c r="D21" s="6"/>
@@ -907,20 +908,19 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_340</t>
+          <t xml:space="preserve">multiple_188</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Determine the winner in a Poker game with John having a Hand of 8♥, 10♥, J♥, Q♥, K♥ and Mike having 9♠, J♠, 10♠, Q♠, K♠.</t>
+          <t xml:space="preserve">Find the grocery store closest to Berkeley that has at least a 4.5 star rating, selling tomatoes and also pet food.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">player1 = John
-hand1 = 8♥, 10♥, J♥, Q♥, K♥
-player2 = Mike
-hand2 = 9♠, J♠, 10♠, Q♠, K♠</t>
+          <t xml:space="preserve">my_location = Berkeley
+rating = 4.5
+products = tomatoes, pet food</t>
         </is>
       </c>
       <c r="D22" s="6"/>
@@ -932,19 +932,18 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_188</t>
+          <t xml:space="preserve">simple_python_47</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the grocery store closest to Berkeley that has at least a 4.5 star rating, selling tomatoes and also pet food.</t>
+          <t xml:space="preserve">Find the boiling point and melting point of water under the sea level of 5000m.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">my_location = Berkeley
-rating = 4.5
-products = tomatoes, pet food</t>
+          <t xml:space="preserve">substance = water
+sea_level = 5000</t>
         </is>
       </c>
       <c r="D23" s="6"/>
@@ -956,18 +955,19 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_47</t>
+          <t xml:space="preserve">simple_python_364</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the boiling point and melting point of water under the sea level of 5000m.</t>
+          <t xml:space="preserve">Can I find an Italian restaurant with Gluten-free options near Brooklyn?</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">substance = water
-sea_level = 5000</t>
+          <t xml:space="preserve">location = Brooklyn
+type = Italian
+diet_option = Gluten-free</t>
         </is>
       </c>
       <c r="D24" s="6"/>
@@ -979,18 +979,18 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_170</t>
+          <t xml:space="preserve">multiple_43</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the player stats of Cristiano Ronaldo in the 2019-2020 season</t>
+          <t xml:space="preserve">What is the energy produced by 5 mol of glucose (C6H12O6)?</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_name = Cristiano Ronaldo
-season = 2019-2020</t>
+          <t xml:space="preserve">mols = 5
+substance = C6H12O6</t>
         </is>
       </c>
       <c r="D25" s="6"/>
@@ -1002,19 +1002,18 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_364</t>
+          <t xml:space="preserve">simple_python_201</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can I find an Italian restaurant with Gluten-free options near Brooklyn?</t>
+          <t xml:space="preserve">Estimate the population of pandas in the wild in China.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Brooklyn
-type = Italian
-diet_option = Gluten-free</t>
+          <t xml:space="preserve">species = pandas
+country = China</t>
         </is>
       </c>
       <c r="D26" s="6"/>
@@ -1026,18 +1025,18 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_43</t>
+          <t xml:space="preserve">multiple_87</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the energy produced by 5 mol of glucose (C6H12O6)?</t>
+          <t xml:space="preserve">Find the latest update or patch for the game 'Cyberpunk 2077' on Xbox platform.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mols = 5
-substance = C6H12O6</t>
+          <t xml:space="preserve">game = Cyberpunk 2077
+platform = Xbox</t>
         </is>
       </c>
       <c r="D27" s="6"/>
@@ -1049,18 +1048,19 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_201</t>
+          <t xml:space="preserve">simple_python_390</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimate the population of pandas in the wild in China.</t>
+          <t xml:space="preserve">Convert 150 Euros to Canadian dollars.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">species = pandas
-country = China</t>
+          <t xml:space="preserve">amount = 150
+from_currency = Euros
+to_currency = Canadian dollars</t>
         </is>
       </c>
       <c r="D28" s="6"/>
@@ -1072,17 +1072,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_56</t>
+          <t xml:space="preserve">multiple_79</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the names of proteins found in the plasma membrane?</t>
+          <t xml:space="preserve">Find art exhibitions for the upcoming month in the Museum of Modern Art, New York.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cell_compartment = plasma membrane</t>
+          <t xml:space="preserve">museum_name = Museum of Modern Art, New York</t>
         </is>
       </c>
       <c r="D29" s="6"/>
@@ -1094,18 +1094,18 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_87</t>
+          <t xml:space="preserve">simple_python_62</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the latest update or patch for the game 'Cyberpunk 2077' on Xbox platform.</t>
+          <t xml:space="preserve">Analyze the DNA sequence 'AGTCGATCGAACGTACGTACG' for any potential substitution mutations based on a reference sequence 'AGTCCATCGAACGTACGTACG'.</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game = Cyberpunk 2077
-platform = Xbox</t>
+          <t xml:space="preserve">sequence = AGTCGATCGAACGTACGTACG
+reference_sequence = AGTCCATCGAACGTACGTACG</t>
         </is>
       </c>
       <c r="D30" s="6"/>
@@ -1117,19 +1117,18 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_390</t>
+          <t xml:space="preserve">multiple_72</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert 150 Euros to Canadian dollars.</t>
+          <t xml:space="preserve">What was the population of California in 1970?</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">amount = 150
-from_currency = Euros
-to_currency = Canadian dollars</t>
+          <t xml:space="preserve">state = California
+year = 1970</t>
         </is>
       </c>
       <c r="D31" s="6"/>
@@ -1141,17 +1140,18 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_79</t>
+          <t xml:space="preserve">simple_python_244</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find art exhibitions for the upcoming month in the Museum of Modern Art, New York.</t>
+          <t xml:space="preserve">What year was the law of universal gravitation published by Isaac Newton?</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">museum_name = Museum of Modern Art, New York</t>
+          <t xml:space="preserve">author = Isaac Newton
+work_title = the law of universal gravitation</t>
         </is>
       </c>
       <c r="D32" s="6"/>
@@ -1163,18 +1163,18 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_62</t>
+          <t xml:space="preserve">simple_python_318</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analyze the DNA sequence 'AGTCGATCGAACGTACGTACG' for any potential substitution mutations based on a reference sequence 'AGTCCATCGAACGTACGTACG'.</t>
+          <t xml:space="preserve">What is the FIFA ranking of Germany's men soccer team for the year 2021?</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sequence = AGTCGATCGAACGTACGTACG
-reference_sequence = AGTCCATCGAACGTACGTACG</t>
+          <t xml:space="preserve">team_name = Germany
+year = 2021</t>
         </is>
       </c>
       <c r="D33" s="6"/>
@@ -1186,18 +1186,19 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_72</t>
+          <t xml:space="preserve">multiple_85</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What was the population of California in 1970?</t>
+          <t xml:space="preserve">Get the soccer scores for Real Madrid games in La Liga for the last 5 rounds.</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">state = California
-year = 1970</t>
+          <t xml:space="preserve">team = Real Madrid
+league = La Liga
+rounds = 5</t>
         </is>
       </c>
       <c r="D34" s="6"/>
@@ -1209,18 +1210,18 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_244</t>
+          <t xml:space="preserve">simple_python_320</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What year was the law of universal gravitation published by Isaac Newton?</t>
+          <t xml:space="preserve">Fetch the basketball league standings, where Golden State Warriors stand in current 2022-2023 season with details</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">author = Isaac Newton
-work_title = the law of universal gravitation</t>
+          <t xml:space="preserve">team = Golden State Warriors
+season = 2022-2023</t>
         </is>
       </c>
       <c r="D35" s="6"/>
@@ -1232,18 +1233,19 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_318</t>
+          <t xml:space="preserve">multiple_164</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the FIFA ranking of Germany's men soccer team for the year 2021?</t>
+          <t xml:space="preserve">What's the retail price of a Fender American Professional II Stratocaster in Rosewood Finish?</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_name = Germany
-year = 2021</t>
+          <t xml:space="preserve">brand = Fender
+model = American Professional II Stratocaster
+finish = Rosewood</t>
         </is>
       </c>
       <c r="D36" s="6"/>
@@ -1255,19 +1257,18 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_85</t>
+          <t xml:space="preserve">simple_python_69</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the soccer scores for Real Madrid games in La Liga for the last 5 rounds.</t>
+          <t xml:space="preserve">Find out the population and species of turtles in Mississippi river in 2020.</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team = Real Madrid
-league = La Liga
-rounds = 5</t>
+          <t xml:space="preserve">location = Mississippi river
+year = 2020</t>
         </is>
       </c>
       <c r="D37" s="6"/>
@@ -1279,20 +1280,19 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_136</t>
+          <t xml:space="preserve">multiple_84</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the compound interest for an investment of $10000 with an annual interest rate of 5% compounded monthly for 5 years.</t>
+          <t xml:space="preserve">Give me the top 10 goal scorers in the UEFA Champions League from Barcelona team.</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">principal = 10000
-annual_rate = 5
-compounding_freq = monthly
-time_in_years = 5</t>
+          <t xml:space="preserve">competition = UEFA Champions League
+team = Barcelona
+number = 10</t>
         </is>
       </c>
       <c r="D38" s="6"/>
@@ -1304,19 +1304,19 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_164</t>
+          <t xml:space="preserve">simple_python_162</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the retail price of a Fender American Professional II Stratocaster in Rosewood Finish?</t>
+          <t xml:space="preserve">Generate a customized law contract between John and Alice for rental agreement in California.</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand = Fender
-model = American Professional II Stratocaster
-finish = Rosewood</t>
+          <t xml:space="preserve">parties = John, Alice
+contract_type = rental agreement
+location = California</t>
         </is>
       </c>
       <c r="D39" s="6"/>
@@ -1328,18 +1328,19 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_69</t>
+          <t xml:space="preserve">simple_python_356</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find out the population and species of turtles in Mississippi river in 2020.</t>
+          <t xml:space="preserve">Find me a recipe that serves 2 people, is vegan, and takes under 30 minutes to prepare.</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Mississippi river
-year = 2020</t>
+          <t xml:space="preserve">servings = 2
+diet = vegan
+prep_time = 30</t>
         </is>
       </c>
       <c r="D40" s="6"/>
@@ -1351,19 +1352,18 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_84</t>
+          <t xml:space="preserve">multiple_19</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give me the top 10 goal scorers in the UEFA Champions League from Barcelona team.</t>
+          <t xml:space="preserve">What are the three great Schism in Christianity history?</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">competition = UEFA Champions League
-team = Barcelona
-number = 10</t>
+          <t xml:space="preserve">religion = Christianity
+count = three</t>
         </is>
       </c>
       <c r="D41" s="6"/>
@@ -1375,19 +1375,19 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_162</t>
+          <t xml:space="preserve">simple_python_399</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate a customized law contract between John and Alice for rental agreement in California.</t>
+          <t xml:space="preserve">Find me the best Italian restaurants in New York City with average customer ratings of more than 4 and accepts credit cards.</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">parties = John, Alice
-contract_type = rental agreement
-location = California</t>
+          <t xml:space="preserve">location = New York City
+cuisine = Italian
+rating = 4</t>
         </is>
       </c>
       <c r="D42" s="6"/>
